--- a/RegisterTestData.xlsx
+++ b/RegisterTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313FF662-D14A-4E81-9877-AEAB7CAFFB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F4EE01-2ED5-4358-994F-3633A26D79FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{94FF2D4F-40CF-40A7-B7CF-5A68C7647CD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{94FF2D4F-40CF-40A7-B7CF-5A68C7647CD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -685,9 +688,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -725,7 +728,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -831,7 +834,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -973,7 +976,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -982,21 +985,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E82345-A358-404B-A455-EF1E0686D503}">
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="33.21875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.6640625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="20.21875" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="11.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1028,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>55</v>
       </c>
@@ -1054,7 +1057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>58</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>60</v>
       </c>
@@ -1112,7 +1115,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>62</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>106</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>4</v>
       </c>
@@ -1226,7 +1229,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>5</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>115</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>6</v>
       </c>
@@ -1313,7 +1316,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>7</v>
       </c>
@@ -1342,7 +1345,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>9</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>13</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
@@ -1487,7 +1490,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
@@ -1514,7 +1517,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>16</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
@@ -1572,7 +1575,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>18</v>
       </c>
@@ -1601,7 +1604,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>19</v>
       </c>
@@ -1630,7 +1633,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>21</v>
       </c>
@@ -1659,7 +1662,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>23</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>24</v>
       </c>
@@ -1717,7 +1720,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>26</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>28</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>29</v>
       </c>
@@ -1829,7 +1832,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>30</v>
       </c>
@@ -1858,7 +1861,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>31</v>
       </c>
@@ -1887,7 +1890,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>33</v>
       </c>
@@ -1916,7 +1919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
@@ -1945,7 +1948,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>36</v>
       </c>
@@ -1974,7 +1977,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>37</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>39</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>41</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>163</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>112</v>
@@ -2090,7 +2093,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>42</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
